--- a/data/trans_camb/P6904-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 25,53</t>
+          <t>-9,66; 27,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 27,99</t>
+          <t>-9,47; 27,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 28,63</t>
+          <t>-9,19; 29,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 22,43</t>
+          <t>-17,55; 26,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 36,99</t>
+          <t>-3,2; 35,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 30,72</t>
+          <t>-5,22; 29,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 19,38</t>
+          <t>-7,03; 19,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 26,18</t>
+          <t>-2,06; 25,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 24,28</t>
+          <t>-0,39; 25,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 100,29</t>
+          <t>-23,13; 106,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 105,48</t>
+          <t>-24,21; 104,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 109,57</t>
+          <t>-21,91; 108,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,49; 92,65</t>
+          <t>-42,66; 111,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 152,15</t>
+          <t>-8,43; 154,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 145,66</t>
+          <t>-11,95; 131,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 70,66</t>
+          <t>-17,54; 68,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 91,87</t>
+          <t>-4,51; 90,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 89,48</t>
+          <t>-1,67; 91,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 46,54</t>
+          <t>6,04; 49,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 54,58</t>
+          <t>6,59; 53,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 37,34</t>
+          <t>-1,63; 37,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 4,16</t>
+          <t>-45,87; 2,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 41,06</t>
+          <t>-6,61; 42,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 22,04</t>
+          <t>-17,79; 26,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 21,81</t>
+          <t>-13,13; 19,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 41,99</t>
+          <t>8,51; 42,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 24,99</t>
+          <t>-3,24; 25,8</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 381,85</t>
+          <t>13,67; 424,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 442,22</t>
+          <t>23,59; 427,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 321,37</t>
+          <t>-7,18; 306,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,63; 16,8</t>
+          <t>-86,41; 16,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 113,69</t>
+          <t>-9,81; 128,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 67,37</t>
+          <t>-32,31; 81,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 90,06</t>
+          <t>-31,37; 73,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,39; 168,77</t>
+          <t>21,56; 161,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 96,5</t>
+          <t>-9,1; 98,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 3,9</t>
+          <t>-27,18; 3,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 7,62</t>
+          <t>-22,64; 7,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 15,37</t>
+          <t>-16,55; 15,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 34,6</t>
+          <t>-25,33; 31,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 50,36</t>
+          <t>-25,07; 49,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 53,16</t>
+          <t>-6,09; 52,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 5,54</t>
+          <t>-21,22; 4,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 10,86</t>
+          <t>-20,51; 9,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 16,86</t>
+          <t>-10,33; 18,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 7,24</t>
+          <t>-38,48; 5,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 13,07</t>
+          <t>-32,87; 13,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 25,46</t>
+          <t>-23,96; 26,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 103,52</t>
+          <t>-34,14; 89,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 155,72</t>
+          <t>-37,8; 135,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 171,83</t>
+          <t>-7,02; 150,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 9,3</t>
+          <t>-31,14; 7,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 18,81</t>
+          <t>-31,0; 17,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 30,32</t>
+          <t>-14,95; 31,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 15,14</t>
+          <t>-6,99; 15,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 17,1</t>
+          <t>-4,98; 16,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 20,17</t>
+          <t>-3,71; 19,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 15,9</t>
+          <t>-20,43; 16,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 30,97</t>
+          <t>-2,78; 30,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 22,81</t>
+          <t>-10,56; 19,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 11,16</t>
+          <t>-8,17; 10,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 18,33</t>
+          <t>-0,57; 16,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 15,75</t>
+          <t>-3,1; 14,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 27,94</t>
+          <t>-11,23; 28,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 32,74</t>
+          <t>-8,03; 29,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 37,27</t>
+          <t>-5,97; 35,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 33,79</t>
+          <t>-29,99; 35,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 67,24</t>
+          <t>-3,6; 68,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 52,56</t>
+          <t>-16,2; 40,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 20,43</t>
+          <t>-12,88; 19,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 34,53</t>
+          <t>-0,89; 31,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 29,85</t>
+          <t>-5,23; 26,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 28,08</t>
+          <t>-12,85; 27,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 32,84</t>
+          <t>-3,47; 33,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,13; 46,18</t>
+          <t>8,71; 45,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 26,6</t>
+          <t>-13,39; 23,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 29,33</t>
+          <t>-8,33; 28,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 36,64</t>
+          <t>2,65; 35,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 21,39</t>
+          <t>-6,29; 21,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 24,81</t>
+          <t>0,67; 25,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,71; 36,8</t>
+          <t>12,02; 37,71</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 70,4</t>
+          <t>-21,76; 65,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 83,87</t>
+          <t>-6,08; 84,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17,96; 117,74</t>
+          <t>15,62; 119,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 48,57</t>
+          <t>-19,0; 43,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 58,56</t>
+          <t>-10,25; 53,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,61; 68,99</t>
+          <t>2,8; 67,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 42,38</t>
+          <t>-10,72; 41,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,12; 50,56</t>
+          <t>1,12; 52,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19,04; 75,34</t>
+          <t>18,43; 77,76</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,31</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,45</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,74</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,39</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,68; 10,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,07; 14,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,59; 16,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,06; 8,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,34; 24,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,85; 25,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,55; 7,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,89; 16,14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,93; 18,53</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,17%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,45; 21,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,2; 29,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,79; 33,37</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,56; 18,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,71; 51,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,63; 53,91</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,52; 16,0</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,09; 32,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,52; 37,29</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>7,31</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>9,25</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>15,45</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>13,74</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>10,39</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>11,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-5,25; 10,3</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 13,99</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 16,46</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-10,03; 9,21</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6,56; 24,63</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>5,9; 25,79</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 7,42</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 16,13</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>6,19; 18,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-0,17%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>29,86%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>26,55%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-9,27; 20,97</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-1,45; 27,9</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>2,88; 33,9</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-17,86; 19,86</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>11,58; 54,02</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>10,8; 58,28</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-7,82; 15,19</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>8,28; 32,51</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>11,24; 37,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P6904-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,62</t>
+          <t>9,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,39</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,55</t>
+          <t>10,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 27,15</t>
+          <t>-9,96; 25,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 27,92</t>
+          <t>-10,65; 27,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 29,91</t>
+          <t>-9,47; 28,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 26,16</t>
+          <t>-20,7; 22,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 35,5</t>
+          <t>-3,63; 37,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 29,69</t>
+          <t>-4,83; 29,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 19,19</t>
+          <t>-8,05; 18,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 25,83</t>
+          <t>-2,47; 27,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 25,3</t>
+          <t>-2,42; 23,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 106,84</t>
+          <t>-25,22; 95,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 104,96</t>
+          <t>-25,2; 102,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 108,75</t>
+          <t>-22,54; 105,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 111,12</t>
+          <t>-50,05; 91,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 154,0</t>
+          <t>-11,05; 162,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 131,97</t>
+          <t>-11,21; 131,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 68,13</t>
+          <t>-20,32; 64,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 90,2</t>
+          <t>-5,56; 95,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 91,02</t>
+          <t>-6,71; 80,53</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,29</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,83</t>
+          <t>10,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 49,28</t>
+          <t>4,13; 49,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 53,16</t>
+          <t>7,51; 54,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 37,7</t>
+          <t>-2,66; 36,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 2,87</t>
+          <t>-43,74; 2,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 42,16</t>
+          <t>-4,97; 40,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 26,47</t>
+          <t>-16,21; 24,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 19,62</t>
+          <t>-13,29; 20,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 42,13</t>
+          <t>7,74; 42,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 25,8</t>
+          <t>-4,6; 24,77</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 424,04</t>
+          <t>7,77; 406,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,59; 427,55</t>
+          <t>20,9; 479,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 306,39</t>
+          <t>-9,05; 293,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,41; 16,68</t>
+          <t>-82,67; 11,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 128,01</t>
+          <t>-11,86; 120,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 81,51</t>
+          <t>-29,72; 74,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 73,52</t>
+          <t>-33,17; 79,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,56; 161,68</t>
+          <t>18,21; 173,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 98,81</t>
+          <t>-11,24; 96,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,74</t>
+          <t>23,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>5,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 3,29</t>
+          <t>-26,61; 3,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 7,96</t>
+          <t>-23,27; 7,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 15,6</t>
+          <t>-15,86; 16,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 31,92</t>
+          <t>-22,71; 36,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 49,36</t>
+          <t>-31,01; 49,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 52,41</t>
+          <t>-5,47; 53,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 4,6</t>
+          <t>-20,93; 4,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 9,78</t>
+          <t>-17,34; 9,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 18,36</t>
+          <t>-8,45; 17,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,34%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 5,83</t>
+          <t>-36,89; 8,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 13,4</t>
+          <t>-33,84; 11,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 26,96</t>
+          <t>-22,81; 29,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 89,75</t>
+          <t>-32,07; 111,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 135,97</t>
+          <t>-48,56; 144,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 150,84</t>
+          <t>-6,29; 165,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 7,67</t>
+          <t>-31,01; 8,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 17,01</t>
+          <t>-26,34; 17,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 31,84</t>
+          <t>-13,03; 30,47</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>10,18</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>7,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 15,26</t>
+          <t>-7,41; 15,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 16,34</t>
+          <t>-4,98; 17,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 19,12</t>
+          <t>-1,23; 21,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 16,65</t>
+          <t>-19,56; 17,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 30,83</t>
+          <t>-1,94; 31,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 19,0</t>
+          <t>-10,92; 21,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 10,7</t>
+          <t>-8,9; 11,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 16,96</t>
+          <t>0,06; 17,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 14,46</t>
+          <t>-0,39; 16,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 28,02</t>
+          <t>-11,77; 28,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 29,78</t>
+          <t>-7,97; 31,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 35,64</t>
+          <t>-0,96; 38,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 35,0</t>
+          <t>-28,57; 35,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 68,54</t>
+          <t>-2,83; 70,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 40,45</t>
+          <t>-16,55; 46,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 19,54</t>
+          <t>-14,16; 20,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 31,59</t>
+          <t>0,15; 31,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 26,1</t>
+          <t>-0,63; 31,65</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28,66</t>
+          <t>31,73</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,71</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>19,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 27,26</t>
+          <t>-14,05; 28,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 33,39</t>
+          <t>-3,03; 32,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,71; 45,97</t>
+          <t>14,76; 47,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 23,74</t>
+          <t>-14,05; 24,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 28,47</t>
+          <t>-4,96; 29,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 35,8</t>
+          <t>-4,4; 23,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 21,04</t>
+          <t>-6,41; 22,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 25,76</t>
+          <t>0,19; 25,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,02; 37,71</t>
+          <t>8,3; 30,26</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 65,51</t>
+          <t>-24,39; 70,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 84,07</t>
+          <t>-4,33; 87,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15,62; 119,05</t>
+          <t>24,63; 126,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 43,29</t>
+          <t>-18,89; 44,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 53,17</t>
+          <t>-6,25; 54,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,8; 67,96</t>
+          <t>-5,96; 46,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 41,38</t>
+          <t>-10,87; 43,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,12; 52,6</t>
+          <t>0,35; 52,53</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18,43; 77,76</t>
+          <t>13,84; 63,04</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11,45</t>
+          <t>10,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 10,44</t>
+          <t>-4,44; 10,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,07; 14,69</t>
+          <t>0,59; 15,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,34</t>
+          <t>3,99; 18,41</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 8,83</t>
+          <t>-9,82; 9,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,34; 24,1</t>
+          <t>5,95; 24,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,85; 25,4</t>
+          <t>1,18; 17,61</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 7,75</t>
+          <t>-4,35; 7,32</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,89; 16,14</t>
+          <t>4,77; 16,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,93; 18,53</t>
+          <t>4,91; 15,34</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 21,19</t>
+          <t>-8,12; 21,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,2; 29,9</t>
+          <t>1,06; 30,57</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2,79; 33,37</t>
+          <t>7,19; 37,8</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 18,63</t>
+          <t>-17,65; 19,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,71; 51,4</t>
+          <t>10,39; 52,6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,63; 53,91</t>
+          <t>2,1; 38,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 16,0</t>
+          <t>-7,96; 14,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9,09; 32,63</t>
+          <t>9,31; 32,96</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10,52; 37,29</t>
+          <t>9,1; 31,35</t>
         </is>
       </c>
     </row>
